--- a/003/xy_003_data.xlsx
+++ b/003/xy_003_data.xlsx
@@ -584,7 +584,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:04</t>
+          <t>25/09/2026 01:16</t>
         </is>
       </c>
     </row>

--- a/003/xy_003_data.xlsx
+++ b/003/xy_003_data.xlsx
@@ -496,7 +496,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Income predicts longevity, with sharply diminishing returns.</t>
+          <t>Income predicts longevity, with sharply diminishing returns in dollars.</t>
         </is>
       </c>
     </row>
@@ -524,7 +524,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GDP per capita (US$, World Bank)</t>
+          <t>GDP per capita (PPP $, World Bank)</t>
         </is>
       </c>
     </row>
@@ -536,7 +536,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GDP per capita, current US$, 2022, World Bank NY.GDP.PCAP.CD, all countries with data</t>
+          <t>GDP per capita, PPP, current international $, 2022, World Bank NY.GDP.PCAP.PP.CD, all countries with data</t>
         </is>
       </c>
     </row>
@@ -548,7 +548,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>World Bank NY.GDP.PCAP.CD (2022)</t>
+          <t>World Bank NY.GDP.PCAP.PP.CD (2022)</t>
         </is>
       </c>
     </row>
@@ -560,7 +560,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://data.worldbank.org/indicator/NY.GDP.PCAP.CD</t>
+          <t>https://data.worldbank.org/indicator/NY.GDP.PCAP.PP.CD</t>
         </is>
       </c>
     </row>
@@ -584,7 +584,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -684,7 +684,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 01:16</t>
+          <t>25/09/2026 02:03</t>
         </is>
       </c>
     </row>
@@ -787,11 +787,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C209"/>
+  <dimension ref="A1:C199"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
     <col width="34" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
@@ -803,7 +803,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>GDP per capita (US$, World Bank)</t>
+          <t>GDP per capita (PPP $, World Bank)</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -819,7 +819,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31000.5713798732</v>
+        <v>41863.2739964163</v>
       </c>
       <c r="C2" t="n">
         <v>76.226</v>
@@ -832,7 +832,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>357.261152798144</v>
+        <v>2122.65936199211</v>
       </c>
       <c r="C3" t="n">
         <v>65.617</v>
@@ -845,7 +845,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3598.53669077341</v>
+        <v>9373.4083091956</v>
       </c>
       <c r="C4" t="n">
         <v>64.246</v>
@@ -858,7 +858,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7756.96188744253</v>
+        <v>22138.4966146921</v>
       </c>
       <c r="C5" t="n">
         <v>78.76900000000001</v>
@@ -871,7 +871,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42414.0590111349</v>
+        <v>68459.2247863103</v>
       </c>
       <c r="C6" t="n">
         <v>84.01600000000001</v>
@@ -884,7 +884,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50759.7590190204</v>
+        <v>75059.7702106115</v>
       </c>
       <c r="C7" t="n">
         <v>80.48699999999999</v>
@@ -897,7 +897,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13962.1894087223</v>
+        <v>29804.0832363731</v>
       </c>
       <c r="C8" t="n">
         <v>75.806</v>
@@ -910,7 +910,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6571.97445545099</v>
+        <v>19158.3333506542</v>
       </c>
       <c r="C9" t="n">
         <v>74.7658536585366</v>
@@ -919,2600 +919,2470 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18017.4589383973</v>
+        <v>29761.8058055292</v>
       </c>
       <c r="C10" t="n">
-        <v>72.752</v>
+        <v>77.483</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20003.3909394099</v>
+        <v>66103.17970669569</v>
       </c>
       <c r="C11" t="n">
-        <v>77.483</v>
+        <v>83.2</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65169.5191118657</v>
+        <v>72286.6352565355</v>
       </c>
       <c r="C12" t="n">
-        <v>83.2</v>
+        <v>81.2951219512195</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52336.7725223758</v>
+        <v>22548.5145929929</v>
       </c>
       <c r="C13" t="n">
-        <v>81.2951219512195</v>
+        <v>74.125</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7770.594223351</v>
+        <v>1101.23579609841</v>
       </c>
       <c r="C14" t="n">
-        <v>74.125</v>
+        <v>62.882</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>301.832255755105</v>
+        <v>68878.9167847285</v>
       </c>
       <c r="C15" t="n">
-        <v>62.882</v>
+        <v>81.74878048780489</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50639.0264882739</v>
+        <v>3843.54493453525</v>
       </c>
       <c r="C16" t="n">
-        <v>81.74878048780489</v>
+        <v>60.475</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1266.42711031904</v>
+        <v>2644.82146127902</v>
       </c>
       <c r="C17" t="n">
-        <v>60.475</v>
+        <v>60.7</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>BGD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>827.330843486661</v>
+        <v>8449.209779313731</v>
       </c>
       <c r="C18" t="n">
-        <v>60.7</v>
+        <v>74.265</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BGD</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2716.48592780431</v>
+        <v>36320.2814407535</v>
       </c>
       <c r="C19" t="n">
-        <v>74.265</v>
+        <v>74.16097560975609</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BHR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13999.9113358453</v>
+        <v>61667.8791526737</v>
       </c>
       <c r="C20" t="n">
-        <v>74.16097560975609</v>
+        <v>80.992</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHR</t>
+          <t>BHS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30470.5219276023</v>
+        <v>36785.5703317271</v>
       </c>
       <c r="C21" t="n">
-        <v>80.992</v>
+        <v>74.491</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>BIH</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34957.1613279737</v>
+        <v>21651.3043527017</v>
       </c>
       <c r="C22" t="n">
-        <v>74.491</v>
+        <v>76.777</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BIH</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7655.59421024383</v>
+        <v>28424.9893656867</v>
       </c>
       <c r="C23" t="n">
-        <v>76.777</v>
+        <v>74.1033658536585</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7994.64806074889</v>
+        <v>13459.0765078205</v>
       </c>
       <c r="C24" t="n">
-        <v>74.1033658536585</v>
+        <v>72.19</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BMU</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7068.21728043145</v>
+        <v>104909.257552793</v>
       </c>
       <c r="C25" t="n">
-        <v>72.19</v>
+        <v>82.062</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BMU</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>119969.173269085</v>
+        <v>12304.7789380156</v>
       </c>
       <c r="C26" t="n">
-        <v>82.062</v>
+        <v>67.434</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4219.46113742445</v>
+        <v>19873.7032623309</v>
       </c>
       <c r="C27" t="n">
-        <v>67.434</v>
+        <v>74.872</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>BRB</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9281.33334441234</v>
+        <v>21952.2087434223</v>
       </c>
       <c r="C28" t="n">
-        <v>74.872</v>
+        <v>75.676</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BRB</t>
+          <t>BRN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24393.2193483944</v>
+        <v>81788.7819525501</v>
       </c>
       <c r="C29" t="n">
-        <v>75.676</v>
+        <v>72.917</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BRN</t>
+          <t>BTN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>36632.9280952155</v>
+        <v>15061.4232582306</v>
       </c>
       <c r="C30" t="n">
-        <v>72.917</v>
+        <v>72.754</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BTN</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3711.32767981591</v>
+        <v>19973.6684436048</v>
       </c>
       <c r="C31" t="n">
-        <v>72.754</v>
+        <v>68.749</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8328.7090572666</v>
+        <v>64217.0443455227</v>
       </c>
       <c r="C32" t="n">
-        <v>68.749</v>
+        <v>81.0948780487805</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>56496.9275340663</v>
+        <v>94629.7224204886</v>
       </c>
       <c r="C33" t="n">
-        <v>81.0948780487805</v>
+        <v>83.60487804878051</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>97809.095567203</v>
+        <v>30918.9258262719</v>
       </c>
       <c r="C34" t="n">
-        <v>83.60487804878051</v>
+        <v>79.176</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>67627.1417347907</v>
+        <v>23028.4517927066</v>
       </c>
       <c r="C35" t="n">
-        <v>81</v>
+        <v>78.202</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>15399.1044717559</v>
+        <v>6718.37891572875</v>
       </c>
       <c r="C36" t="n">
-        <v>79.176</v>
+        <v>61.562</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>12970.6056414327</v>
+        <v>5188.15515765322</v>
       </c>
       <c r="C37" t="n">
-        <v>78.202</v>
+        <v>62.443</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>2333.37128301259</v>
+        <v>1589.91203243059</v>
       </c>
       <c r="C38" t="n">
-        <v>61.562</v>
+        <v>60.979</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>1604.87726954895</v>
+        <v>6646.44331964568</v>
       </c>
       <c r="C39" t="n">
-        <v>62.443</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>687.738587554685</v>
+        <v>20854.002999162</v>
       </c>
       <c r="C40" t="n">
-        <v>60.979</v>
+        <v>76.508</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>2620.83804267402</v>
+        <v>3712.34821507981</v>
       </c>
       <c r="C41" t="n">
-        <v>65</v>
+        <v>66.48099999999999</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>6680.44506854481</v>
+        <v>9479.570790166939</v>
       </c>
       <c r="C42" t="n">
-        <v>76.508</v>
+        <v>75.907</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>1533.87755393614</v>
+        <v>26891.9730070246</v>
       </c>
       <c r="C43" t="n">
-        <v>66.48099999999999</v>
+        <v>79.316</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>CUW</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>4323.31362032709</v>
+        <v>28636.1483744106</v>
       </c>
       <c r="C44" t="n">
-        <v>75.907</v>
+        <v>76.729</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CRI</t>
+          <t>CYM</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>13971.7649991294</v>
+        <v>82193.1801927387</v>
       </c>
       <c r="C45" t="n">
-        <v>79.316</v>
+        <v>79.98399999999999</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CUW</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>20057.1404960105</v>
+        <v>55876.3828125</v>
       </c>
       <c r="C46" t="n">
-        <v>76.729</v>
+        <v>80.434</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CYM</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>92937.8838323153</v>
+        <v>52946.9660854462</v>
       </c>
       <c r="C47" t="n">
-        <v>79.98399999999999</v>
+        <v>78.92926829268291</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>33231.05078125</v>
+        <v>69669.6495435563</v>
       </c>
       <c r="C48" t="n">
-        <v>80.434</v>
+        <v>80.60804878048781</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>28282.2236715857</v>
+        <v>6620.28103140186</v>
       </c>
       <c r="C49" t="n">
-        <v>78.92926829268291</v>
+        <v>65.54000000000001</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>DMA</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>50506.5179638543</v>
+        <v>18799.1022306558</v>
       </c>
       <c r="C50" t="n">
-        <v>80.60804878048781</v>
+        <v>71.081</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>3133.25779772463</v>
+        <v>78554.12176179831</v>
       </c>
       <c r="C51" t="n">
-        <v>65.54000000000001</v>
+        <v>81.30487804878049</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DMA</t>
+          <t>DOM</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>9323.660894905621</v>
+        <v>24621.9061494267</v>
       </c>
       <c r="C52" t="n">
-        <v>71.081</v>
+        <v>74.211</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>67781.0940939514</v>
+        <v>15833.5847271335</v>
       </c>
       <c r="C53" t="n">
-        <v>81.30487804878049</v>
+        <v>76.129</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>10104.2464008585</v>
+        <v>15195.6639594842</v>
       </c>
       <c r="C54" t="n">
-        <v>74.211</v>
+        <v>76.577</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>4960.30334332888</v>
+        <v>17524.0240491999</v>
       </c>
       <c r="C55" t="n">
-        <v>76.129</v>
+        <v>71.01000000000001</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>6515.58528418336</v>
+        <v>51482.523634807</v>
       </c>
       <c r="C56" t="n">
-        <v>76.577</v>
+        <v>83.13414634146341</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>4233.30783744856</v>
+        <v>48029.83322897</v>
       </c>
       <c r="C57" t="n">
-        <v>71.01000000000001</v>
+        <v>77.8439024390244</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>30319.4987196616</v>
+        <v>2844.47188098448</v>
       </c>
       <c r="C58" t="n">
-        <v>83.13414634146341</v>
+        <v>66.89700000000001</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>28340.3826549406</v>
+        <v>62133.1375219912</v>
       </c>
       <c r="C59" t="n">
-        <v>77.8439024390244</v>
+        <v>81.18780487804879</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>982.103161502198</v>
+        <v>12980.234013809</v>
       </c>
       <c r="C60" t="n">
-        <v>66.89700000000001</v>
+        <v>67.148</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>50440.560224974</v>
+        <v>57012.0586826676</v>
       </c>
       <c r="C61" t="n">
-        <v>81.18780487804879</v>
+        <v>82.12926829268289</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>5414.12092119088</v>
+        <v>75266.29526904129</v>
       </c>
       <c r="C62" t="n">
-        <v>67.148</v>
+        <v>82.8162292682927</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>FSM</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>40988.6396406579</v>
+        <v>4087.19316400156</v>
       </c>
       <c r="C63" t="n">
-        <v>82.12926829268289</v>
+        <v>66.961</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>67069.39874405089</v>
+        <v>19989.3886367516</v>
       </c>
       <c r="C64" t="n">
-        <v>82.8162292682927</v>
+        <v>67.71299999999999</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FSM</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>3703.66680343222</v>
+        <v>60266.7467325014</v>
       </c>
       <c r="C65" t="n">
-        <v>66.961</v>
+        <v>81.0112195121951</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>8409.207414522791</v>
+        <v>22457.7729614408</v>
       </c>
       <c r="C66" t="n">
-        <v>67.71299999999999</v>
+        <v>74.14100000000001</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>47034.7795621476</v>
+        <v>7207.01563645025</v>
       </c>
       <c r="C67" t="n">
-        <v>81.0112195121951</v>
+        <v>65.246</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>6729.84659930283</v>
+        <v>4061.71755990026</v>
       </c>
       <c r="C68" t="n">
-        <v>74.14100000000001</v>
+        <v>60.432</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>2229.89122654479</v>
+        <v>3066.82429529872</v>
       </c>
       <c r="C69" t="n">
-        <v>65.246</v>
+        <v>64.85899999999999</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>1416.59612011764</v>
+        <v>2785.7846268362</v>
       </c>
       <c r="C70" t="n">
-        <v>60.432</v>
+        <v>63.605</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>836.244875868476</v>
+        <v>18137.114494644</v>
       </c>
       <c r="C71" t="n">
-        <v>64.85899999999999</v>
+        <v>63.355</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>881.602654162231</v>
+        <v>39447.813910406</v>
       </c>
       <c r="C72" t="n">
-        <v>63.605</v>
+        <v>80.7878048780488</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>GRD</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>7589.29964909381</v>
+        <v>17541.2011831673</v>
       </c>
       <c r="C73" t="n">
-        <v>63.355</v>
+        <v>75.151</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>GRL</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>20884.6773436263</v>
+        <v>75708.4296211883</v>
       </c>
       <c r="C74" t="n">
-        <v>80.7878048780488</v>
+        <v>71.230243902439</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GRD</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>10469.3867012856</v>
+        <v>13008.2565459863</v>
       </c>
       <c r="C75" t="n">
-        <v>75.151</v>
+        <v>71.206</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GRL</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>55635.0006491223</v>
+        <v>39704.6761521236</v>
       </c>
       <c r="C76" t="n">
-        <v>71.230243902439</v>
+        <v>69.88800000000001</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>5356.92435887895</v>
+        <v>68590.18587415649</v>
       </c>
       <c r="C77" t="n">
-        <v>71.206</v>
+        <v>83.66097560975609</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GUM</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>41833.1517132825</v>
+        <v>6804.41504589356</v>
       </c>
       <c r="C78" t="n">
-        <v>77.102</v>
+        <v>72.715</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>17913.4928066879</v>
+        <v>42125.1926231817</v>
       </c>
       <c r="C79" t="n">
-        <v>69.88800000000001</v>
+        <v>77.57560975609761</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>HTI</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>48825.0272275805</v>
+        <v>3245.27176023069</v>
       </c>
       <c r="C80" t="n">
-        <v>83.66097560975609</v>
+        <v>63.948</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>3003.28996826399</v>
+        <v>44232.4363539167</v>
       </c>
       <c r="C81" t="n">
-        <v>72.715</v>
+        <v>75.86829268292681</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>18465.531473659</v>
+        <v>14282.6654124401</v>
       </c>
       <c r="C82" t="n">
-        <v>77.57560975609761</v>
+        <v>70.925</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HTI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>1748.40890116803</v>
+        <v>8941.092774475141</v>
       </c>
       <c r="C83" t="n">
-        <v>63.948</v>
+        <v>71.69799999999999</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>18428.028825614</v>
+        <v>138464.829172919</v>
       </c>
       <c r="C84" t="n">
-        <v>75.86829268292681</v>
+        <v>82.509756097561</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>IRN</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>4730.83484836107</v>
+        <v>17542.844026084</v>
       </c>
       <c r="C85" t="n">
-        <v>70.925</v>
+        <v>76.79900000000001</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IMN</t>
+          <t>IRQ</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>88328.548125887</v>
+        <v>14388.8485236797</v>
       </c>
       <c r="C86" t="n">
-        <v>80.956</v>
+        <v>72.03700000000001</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>2279.98145719369</v>
+        <v>76592.3392429534</v>
       </c>
       <c r="C87" t="n">
-        <v>71.69799999999999</v>
+        <v>82.119512195122</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>105190.685952731</v>
+        <v>53616.7140829107</v>
       </c>
       <c r="C88" t="n">
-        <v>82.509756097561</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IRN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>4721.20437099984</v>
+        <v>57260.8945372493</v>
       </c>
       <c r="C89" t="n">
-        <v>76.79900000000001</v>
+        <v>82.7</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IRQ</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>6520.73154560584</v>
+        <v>11885.8863913319</v>
       </c>
       <c r="C90" t="n">
-        <v>72.03700000000001</v>
+        <v>71.48099999999999</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>JOR</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>76376.9599334915</v>
+        <v>10880.9956299022</v>
       </c>
       <c r="C91" t="n">
-        <v>82.119512195122</v>
+        <v>77.08799999999999</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>54947.2091250715</v>
+        <v>49245.964174373</v>
       </c>
       <c r="C92" t="n">
-        <v>82.7</v>
+        <v>83.99634146341459</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>35653.9042103495</v>
+        <v>35889.3953214448</v>
       </c>
       <c r="C93" t="n">
-        <v>82.7</v>
+        <v>73.503</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>6626.47502388538</v>
+        <v>5882.29066433207</v>
       </c>
       <c r="C94" t="n">
-        <v>71.48099999999999</v>
+        <v>63.549</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JOR</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>4754.41362207378</v>
+        <v>6576.46977080639</v>
       </c>
       <c r="C95" t="n">
-        <v>77.08799999999999</v>
+        <v>72.0487804878049</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>KHM</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>35548.2645222433</v>
+        <v>6917.7197730003</v>
       </c>
       <c r="C96" t="n">
-        <v>83.99634146341459</v>
+        <v>70.52800000000001</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>KIR</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>11255.3396437881</v>
+        <v>3349.59804202737</v>
       </c>
       <c r="C97" t="n">
-        <v>73.503</v>
+        <v>66.26900000000001</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>KNA</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>2109.56288513137</v>
+        <v>31865.8304697944</v>
       </c>
       <c r="C98" t="n">
-        <v>63.549</v>
+        <v>70.313</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KGZ</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>1739.72018344174</v>
+        <v>55509.3368761174</v>
       </c>
       <c r="C99" t="n">
-        <v>72.0487804878049</v>
+        <v>82.6804878048781</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KHM</t>
+          <t>KWT</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>2325.03050040841</v>
+        <v>55034.2790289403</v>
       </c>
       <c r="C100" t="n">
-        <v>70.52800000000001</v>
+        <v>80.5878048780488</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KIR</t>
+          <t>LAO</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2078.7648751855</v>
+        <v>8765.051317471631</v>
       </c>
       <c r="C101" t="n">
-        <v>66.26900000000001</v>
+        <v>68.715</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KNA</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>21011.5744209816</v>
+        <v>12290.8925567636</v>
       </c>
       <c r="C102" t="n">
-        <v>70.313</v>
+        <v>78.003</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>34822.4048404971</v>
+        <v>1691.30467616419</v>
       </c>
       <c r="C103" t="n">
-        <v>82.6804878048781</v>
+        <v>61.934</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KWT</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>39981.7691035833</v>
+        <v>12264.4456986569</v>
       </c>
       <c r="C104" t="n">
-        <v>80.5878048780488</v>
+        <v>74.462</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>LAO</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>2046.40440255621</v>
+        <v>24433.7034481087</v>
       </c>
       <c r="C105" t="n">
-        <v>68.715</v>
+        <v>72.67</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LBN</t>
+          <t>LKA</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>3654.35845534878</v>
+        <v>14191.4051912109</v>
       </c>
       <c r="C106" t="n">
-        <v>78.003</v>
+        <v>77.3</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>744.617175237387</v>
+        <v>2760.87343646139</v>
       </c>
       <c r="C107" t="n">
-        <v>61.934</v>
+        <v>56.812</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>5986.63694851258</v>
+        <v>50653.3394443751</v>
       </c>
       <c r="C108" t="n">
-        <v>74.462</v>
+        <v>75.6439024390244</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>12976.1489693474</v>
+        <v>146919.145398495</v>
       </c>
       <c r="C109" t="n">
-        <v>72.67</v>
+        <v>82.9463414634147</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LIE</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>188055.003235348</v>
+        <v>40546.4638799692</v>
       </c>
       <c r="C110" t="n">
-        <v>84.1219512195122</v>
+        <v>74.27804878048779</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LKA</t>
+          <t>MAC</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>3342.63650438046</v>
+        <v>64183.3559914099</v>
       </c>
       <c r="C111" t="n">
-        <v>77.3</v>
+        <v>83.0804878048781</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>1030.12582947757</v>
+        <v>9308.556640625</v>
       </c>
       <c r="C112" t="n">
-        <v>56.812</v>
+        <v>75.161</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>24946.5724005188</v>
+        <v>16442.1034354056</v>
       </c>
       <c r="C113" t="n">
-        <v>75.6439024390244</v>
+        <v>71.54600000000001</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>123719.658915996</v>
+        <v>1716.40079421689</v>
       </c>
       <c r="C114" t="n">
-        <v>82.9463414634147</v>
+        <v>63.068</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>MDV</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>20221.103686109</v>
+        <v>22876.8862033838</v>
       </c>
       <c r="C115" t="n">
-        <v>74.27804878048779</v>
+        <v>80.76000000000001</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>MAC</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>36806.891255461</v>
+        <v>23135.4931593441</v>
       </c>
       <c r="C116" t="n">
-        <v>83.0804878048781</v>
+        <v>73.973</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MHL</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>3463.1376953125</v>
+        <v>7431.2014968892</v>
       </c>
       <c r="C117" t="n">
-        <v>75.161</v>
+        <v>66.72499999999999</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>226052.060664649</v>
+        <v>24212.3733096953</v>
       </c>
       <c r="C118" t="n">
-        <v>85.746</v>
+        <v>74.4248780487805</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>5744.29618434435</v>
+        <v>3013.94334673825</v>
       </c>
       <c r="C119" t="n">
-        <v>71.54600000000001</v>
+        <v>60.035</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>504.059106969168</v>
+        <v>60623.0076694404</v>
       </c>
       <c r="C120" t="n">
-        <v>63.068</v>
+        <v>82.2975609756098</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MDV</t>
+          <t>MMR</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>11786.0191492983</v>
+        <v>5731.02947916374</v>
       </c>
       <c r="C121" t="n">
-        <v>80.76000000000001</v>
+        <v>66.506</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MNE</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>11405.7940469896</v>
+        <v>28049.7293227735</v>
       </c>
       <c r="C122" t="n">
-        <v>73.973</v>
+        <v>76.18780487804879</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MHL</t>
+          <t>MNG</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>6455.6603538189</v>
+        <v>16399.3900820069</v>
       </c>
       <c r="C123" t="n">
-        <v>66.72499999999999</v>
+        <v>71.90073170731711</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>7606.2375253797</v>
+        <v>1581.76710168717</v>
       </c>
       <c r="C124" t="n">
-        <v>74.4248780487805</v>
+        <v>63.011</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>976.914116406452</v>
+        <v>6483.80020315347</v>
       </c>
       <c r="C125" t="n">
-        <v>60.035</v>
+        <v>68.28100000000001</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>35658.8318250199</v>
+        <v>26783.5527116445</v>
       </c>
       <c r="C126" t="n">
-        <v>82.2975609756098</v>
+        <v>73.51463414634151</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MMR</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>1158.05005034332</v>
+        <v>1778.02399491871</v>
       </c>
       <c r="C127" t="n">
-        <v>66.506</v>
+        <v>66.03700000000001</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MNE</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>10038.1849482517</v>
+        <v>34414.4136245222</v>
       </c>
       <c r="C128" t="n">
-        <v>76.18780487804879</v>
+        <v>75.444</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MNG</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>4993.51487463495</v>
+        <v>10661.0118776397</v>
       </c>
       <c r="C129" t="n">
-        <v>71.90073170731711</v>
+        <v>64.19</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MNP</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>23785.754590043</v>
+        <v>1847.58034360869</v>
       </c>
       <c r="C130" t="n">
-        <v>78.53100000000001</v>
+        <v>60.398</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>578.273222184503</v>
+        <v>8303.641931916851</v>
       </c>
       <c r="C131" t="n">
-        <v>63.011</v>
+        <v>54.079</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>1961.28166648869</v>
+        <v>7795.45560731699</v>
       </c>
       <c r="C132" t="n">
-        <v>68.28100000000001</v>
+        <v>74.46299999999999</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>10246.5017455553</v>
+        <v>78630.3599072098</v>
       </c>
       <c r="C133" t="n">
-        <v>73.51463414634151</v>
+        <v>81.6146341463415</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>604.269740360317</v>
+        <v>129914.042717786</v>
       </c>
       <c r="C134" t="n">
-        <v>66.03700000000001</v>
+        <v>82.509756097561</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>11754.5678336248</v>
+        <v>5102.18358728663</v>
       </c>
       <c r="C135" t="n">
-        <v>75.444</v>
+        <v>70.087</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>NRU</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>4349.79908493314</v>
+        <v>12874.2258577781</v>
       </c>
       <c r="C136" t="n">
-        <v>64.19</v>
+        <v>61.93</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>33516.363085906</v>
+        <v>54080.0485491723</v>
       </c>
       <c r="C137" t="n">
-        <v>77.69799999999999</v>
+        <v>81.95853658536581</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>OMN</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>613.614736429298</v>
+        <v>42609.5810436221</v>
       </c>
       <c r="C138" t="n">
-        <v>60.398</v>
+        <v>77.911</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>2899.16047469267</v>
+        <v>5919.33605935593</v>
       </c>
       <c r="C139" t="n">
-        <v>54.079</v>
+        <v>67.417</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2322.89069619459</v>
+        <v>36327.3867449699</v>
       </c>
       <c r="C140" t="n">
-        <v>74.46299999999999</v>
+        <v>79.324</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>59123.318556487</v>
+        <v>16673.6937563476</v>
       </c>
       <c r="C141" t="n">
-        <v>81.6146341463415</v>
+        <v>76.834</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>113122.130765691</v>
+        <v>10129.7407504053</v>
       </c>
       <c r="C142" t="n">
-        <v>82.509756097561</v>
+        <v>69.47199999999999</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>1385.91066002922</v>
+        <v>17415.0224611906</v>
       </c>
       <c r="C143" t="n">
-        <v>70.087</v>
+        <v>68.922</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NRU</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>15309.8345351924</v>
+        <v>4419.49434920144</v>
       </c>
       <c r="C144" t="n">
-        <v>61.93</v>
+        <v>65.274</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>49141.6316294227</v>
+        <v>46777.5524519162</v>
       </c>
       <c r="C145" t="n">
-        <v>81.95853658536581</v>
+        <v>77.1560975609756</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>OMN</t>
+          <t>PRI</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>23223.5829405935</v>
+        <v>45320.1718585525</v>
       </c>
       <c r="C146" t="n">
-        <v>77.911</v>
+        <v>79.42700000000001</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>1538.3228133171</v>
+        <v>45250.0152469537</v>
       </c>
       <c r="C147" t="n">
-        <v>67.417</v>
+        <v>81.63170731707319</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>17378.6070083597</v>
+        <v>16305.6206649067</v>
       </c>
       <c r="C148" t="n">
-        <v>79.324</v>
+        <v>72.319</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>7353.74598721667</v>
+        <v>6162.27222447827</v>
       </c>
       <c r="C149" t="n">
-        <v>76.834</v>
+        <v>76.66200000000001</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>QAT</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>3548.06930572116</v>
+        <v>122901.018274888</v>
       </c>
       <c r="C150" t="n">
-        <v>69.47199999999999</v>
+        <v>81.857</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>13934.951996171</v>
+        <v>41979.4260140907</v>
       </c>
       <c r="C151" t="n">
-        <v>68.922</v>
+        <v>75.1536585365854</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>3102.29409730005</v>
+        <v>40932.71484375</v>
       </c>
       <c r="C152" t="n">
-        <v>65.274</v>
+        <v>72.5456097560976</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>18891.2121169279</v>
+        <v>3195.28136566525</v>
       </c>
       <c r="C153" t="n">
-        <v>77.1560975609756</v>
+        <v>67.52800000000001</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>PRI</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>35353.5613891039</v>
+        <v>71956.6694296826</v>
       </c>
       <c r="C154" t="n">
-        <v>79.42700000000001</v>
+        <v>77.31</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>24620.5197587181</v>
+        <v>3354.84643554688</v>
       </c>
       <c r="C155" t="n">
-        <v>81.63170731707319</v>
+        <v>65.69499999999999</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>6189.10205375331</v>
+        <v>4529.50264399113</v>
       </c>
       <c r="C156" t="n">
-        <v>72.319</v>
+        <v>67.788</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>3799.95527015163</v>
+        <v>144417.646950009</v>
       </c>
       <c r="C157" t="n">
-        <v>76.66200000000001</v>
+        <v>82.89512195121949</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PYF</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>20053.9569369322</v>
+        <v>2496.15153066833</v>
       </c>
       <c r="C158" t="n">
-        <v>83.85899999999999</v>
+        <v>70.40900000000001</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>QAT</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>88701.463352273</v>
+        <v>3143.46625292281</v>
       </c>
       <c r="C159" t="n">
-        <v>81.857</v>
+        <v>61.275</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>15503.4691366242</v>
+        <v>11874.0814242931</v>
       </c>
       <c r="C160" t="n">
-        <v>75.1536585365854</v>
+        <v>71.96899999999999</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>15625.6328125</v>
+        <v>75929.4591270254</v>
       </c>
       <c r="C161" t="n">
-        <v>72.5456097560976</v>
+        <v>85.708</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>1007.05989322914</v>
+        <v>1486.23689665021</v>
       </c>
       <c r="C162" t="n">
-        <v>67.52800000000001</v>
+        <v>53.931</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>38510.2276211037</v>
+        <v>26142.9143111159</v>
       </c>
       <c r="C163" t="n">
-        <v>77.31</v>
+        <v>75.2365853658537</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>1046.24084472656</v>
+        <v>6032.7249522726</v>
       </c>
       <c r="C164" t="n">
-        <v>65.69499999999999</v>
+        <v>69.23699999999999</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1574.0281059306</v>
+        <v>20075.6544534114</v>
       </c>
       <c r="C165" t="n">
-        <v>67.788</v>
+        <v>73.254</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>91227.6970426492</v>
+        <v>41529.408474315</v>
       </c>
       <c r="C166" t="n">
-        <v>82.89512195121949</v>
+        <v>76.9658536585366</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>1877.78104490956</v>
+        <v>52322.1405997493</v>
       </c>
       <c r="C167" t="n">
-        <v>70.40900000000001</v>
+        <v>81.28292682926831</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>860.371067874555</v>
+        <v>66517.6358713011</v>
       </c>
       <c r="C168" t="n">
-        <v>61.275</v>
+        <v>83.0585365853659</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>5074.60050994225</v>
+        <v>10633.7069148254</v>
       </c>
       <c r="C169" t="n">
-        <v>71.96899999999999</v>
+        <v>63.028</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>SXM</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>54264.5837022908</v>
+        <v>48752.9549877316</v>
       </c>
       <c r="C170" t="n">
-        <v>85.708</v>
+        <v>76.18000000000001</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>573.1411657982291</v>
+        <v>29215.6725189214</v>
       </c>
       <c r="C171" t="n">
-        <v>53.931</v>
+        <v>74.509756097561</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>SYR</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>10024.8191112596</v>
+        <v>4905.15252202552</v>
       </c>
       <c r="C172" t="n">
-        <v>75.2365853658537</v>
+        <v>72.79000000000001</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>TCA</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>2389.73729784737</v>
+        <v>30216.0346068372</v>
       </c>
       <c r="C173" t="n">
-        <v>69.23699999999999</v>
+        <v>77.91800000000001</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>6084.43876736445</v>
+        <v>2623.702025997</v>
       </c>
       <c r="C174" t="n">
-        <v>73.254</v>
+        <v>54.528</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>21317.7943982363</v>
+        <v>3305.92970304109</v>
       </c>
       <c r="C175" t="n">
-        <v>76.9658536585366</v>
+        <v>62.292</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>28360.3041467268</v>
+        <v>22245.6387597542</v>
       </c>
       <c r="C176" t="n">
-        <v>81.28292682926831</v>
+        <v>75.291</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>54836.8907235124</v>
+        <v>4513.4597158968</v>
       </c>
       <c r="C177" t="n">
-        <v>83.0585365853659</v>
+        <v>71.562</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>TKM</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>3894.1620089869</v>
+        <v>18148.7189785918</v>
       </c>
       <c r="C178" t="n">
-        <v>63.028</v>
+        <v>69.913</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SXM</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>37793.1283815826</v>
+        <v>5728.90346523347</v>
       </c>
       <c r="C179" t="n">
-        <v>76.18000000000001</v>
+        <v>67.36799999999999</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>TON</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>16682.6990711785</v>
+        <v>7295.94922827877</v>
       </c>
       <c r="C180" t="n">
-        <v>74.509756097561</v>
+        <v>72.63500000000001</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SYR</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>1056.78264718197</v>
+        <v>32973.632075038</v>
       </c>
       <c r="C181" t="n">
-        <v>72.79000000000001</v>
+        <v>73.331</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>TCA</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>31280.5418020808</v>
+        <v>13616.380720945</v>
       </c>
       <c r="C182" t="n">
-        <v>77.91800000000001</v>
+        <v>76.05</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>966.036468278568</v>
+        <v>39919.1608756567</v>
       </c>
       <c r="C183" t="n">
-        <v>54.528</v>
+        <v>77.59099999999999</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>TUV</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>1071.61539220759</v>
+        <v>5403.33289042089</v>
       </c>
       <c r="C184" t="n">
-        <v>62.292</v>
+        <v>66.852</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>6910.00995211206</v>
+        <v>3799.26000976563</v>
       </c>
       <c r="C185" t="n">
-        <v>75.291</v>
+        <v>66.879</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>1052.17949484894</v>
+        <v>2918.71512173871</v>
       </c>
       <c r="C186" t="n">
-        <v>71.562</v>
+        <v>67.675</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TKM</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>5198.18947409551</v>
+        <v>14767.73046875</v>
       </c>
       <c r="C187" t="n">
-        <v>69.913</v>
+        <v>72.658</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>URY</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>2343.24955542816</v>
+        <v>33033.5719368346</v>
       </c>
       <c r="C188" t="n">
-        <v>67.36799999999999</v>
+        <v>76.468</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TON</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>5298.01942454298</v>
+        <v>78008.6895811877</v>
       </c>
       <c r="C189" t="n">
-        <v>72.63500000000001</v>
+        <v>77.4341463414634</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>20750.5202434652</v>
+        <v>10809.1380396181</v>
       </c>
       <c r="C190" t="n">
-        <v>73.331</v>
+        <v>72.14700000000001</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>VCT</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>3707.29283414381</v>
+        <v>18032.4150562634</v>
       </c>
       <c r="C191" t="n">
-        <v>76.05</v>
+        <v>71.191</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>VIR</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>10897.8397861365</v>
+        <v>49785.1412220186</v>
       </c>
       <c r="C192" t="n">
-        <v>77.59099999999999</v>
+        <v>80.319512195122</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TUV</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>5414.74642912412</v>
+        <v>13902.9499867089</v>
       </c>
       <c r="C193" t="n">
-        <v>66.852</v>
+        <v>74.502</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>VUT</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>1207.52062988281</v>
+        <v>3918.73096260725</v>
       </c>
       <c r="C194" t="n">
-        <v>66.879</v>
+        <v>71.30200000000001</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>963.0673141171779</v>
+        <v>6908.96157777708</v>
       </c>
       <c r="C195" t="n">
-        <v>67.675</v>
+        <v>71.55</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>XKX</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>4199.6708984375</v>
+        <v>13948.6857891476</v>
       </c>
       <c r="C196" t="n">
-        <v>72.658</v>
+        <v>77.623</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>URY</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>21009.2883798725</v>
+        <v>14746.7103701698</v>
       </c>
       <c r="C197" t="n">
-        <v>76.468</v>
+        <v>65.45399999999999</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>78008.6895811877</v>
+        <v>3840.115825721</v>
       </c>
       <c r="C198" t="n">
-        <v>77.4341463414634</v>
+        <v>65.279</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>2698.60262953369</v>
+        <v>5395.02452868174</v>
       </c>
       <c r="C199" t="n">
-        <v>72.14700000000001</v>
-      </c>
-    </row>
-    <row r="200">
-      <c r="A200" t="inlineStr">
-        <is>
-          <t>VCT</t>
-        </is>
-      </c>
-      <c r="B200" t="n">
-        <v>9693.55867833025</v>
-      </c>
-      <c r="C200" t="n">
-        <v>71.191</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>3155.04190923584</v>
-      </c>
-      <c r="C201" t="n">
-        <v>72.566</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>VIR</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>44320.909185774</v>
-      </c>
-      <c r="C202" t="n">
-        <v>80.319512195122</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>VNM</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>4147.69777213621</v>
-      </c>
-      <c r="C203" t="n">
-        <v>74.502</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>VUT</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>3679.53524327491</v>
-      </c>
-      <c r="C204" t="n">
-        <v>71.30200000000001</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>WSM</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>4132.44717734444</v>
-      </c>
-      <c r="C205" t="n">
-        <v>71.55</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>XKX</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>5298.1473871027</v>
-      </c>
-      <c r="C206" t="n">
-        <v>77.623</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>ZAF</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>6534.24867783397</v>
-      </c>
-      <c r="C207" t="n">
-        <v>65.45399999999999</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>ZMB</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>1447.12310138035</v>
-      </c>
-      <c r="C208" t="n">
-        <v>65.279</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>ZWE</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>2536.40197087505</v>
-      </c>
-      <c r="C209" t="n">
         <v>62.36</v>
       </c>
     </row>
@@ -3527,11 +3397,11 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B210"/>
+  <dimension ref="A1:B200"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
-    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="36" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -3542,7 +3412,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>GDP per capita (US$, World Bank)</t>
+          <t>GDP per capita (PPP $, World Bank)</t>
         </is>
       </c>
     </row>
@@ -3553,7 +3423,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>31000.5713798732</v>
+        <v>41863.2739964163</v>
       </c>
     </row>
     <row r="3">
@@ -3563,7 +3433,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>357.261152798144</v>
+        <v>2122.65936199211</v>
       </c>
     </row>
     <row r="4">
@@ -3573,7 +3443,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3598.53669077341</v>
+        <v>9373.4083091956</v>
       </c>
     </row>
     <row r="5">
@@ -3583,7 +3453,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>7756.96188744253</v>
+        <v>22138.4966146921</v>
       </c>
     </row>
     <row r="6">
@@ -3593,7 +3463,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>42414.0590111349</v>
+        <v>68459.2247863103</v>
       </c>
     </row>
     <row r="7">
@@ -3603,7 +3473,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>50759.7590190204</v>
+        <v>75059.7702106115</v>
       </c>
     </row>
     <row r="8">
@@ -3613,7 +3483,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>13962.1894087223</v>
+        <v>29804.0832363731</v>
       </c>
     </row>
     <row r="9">
@@ -3623,2017 +3493,1917 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>6571.97445545099</v>
+        <v>19158.3333506542</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>ASM</t>
+          <t>ATG</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>18017.4589383973</v>
+        <v>29761.8058055292</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>ATG</t>
+          <t>AUS</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>20003.3909394099</v>
+        <v>66103.17970669569</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AUS</t>
+          <t>AUT</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>65169.5191118657</v>
+        <v>72286.6352565355</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AUT</t>
+          <t>AZE</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>52336.7725223758</v>
+        <v>22548.5145929929</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>AZE</t>
+          <t>BDI</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>7770.594223351</v>
+        <v>1101.23579609841</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>BDI</t>
+          <t>BEL</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>301.832255755105</v>
+        <v>68878.9167847285</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>BEL</t>
+          <t>BEN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>50639.0264882739</v>
+        <v>3843.54493453525</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>BEN</t>
+          <t>BFA</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1266.42711031904</v>
+        <v>2644.82146127902</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>BFA</t>
+          <t>BGD</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>827.330843486661</v>
+        <v>8449.209779313731</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>BGD</t>
+          <t>BGR</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>2716.48592780431</v>
+        <v>36320.2814407535</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>BGR</t>
+          <t>BHR</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>13999.9113358453</v>
+        <v>61667.8791526737</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>BHR</t>
+          <t>BHS</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>30470.5219276023</v>
+        <v>36785.5703317271</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>BHS</t>
+          <t>BIH</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>34957.1613279737</v>
+        <v>21651.3043527017</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>BIH</t>
+          <t>BLR</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>7655.59421024383</v>
+        <v>28424.9893656867</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>BLR</t>
+          <t>BLZ</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>7994.64806074889</v>
+        <v>13459.0765078205</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>BLZ</t>
+          <t>BMU</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>7068.21728043145</v>
+        <v>104909.257552793</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>BMU</t>
+          <t>BOL</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>119969.173269085</v>
+        <v>12304.7789380156</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>BOL</t>
+          <t>BRA</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>4219.46113742445</v>
+        <v>19873.7032623309</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>BRA</t>
+          <t>BRB</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>9281.33334441234</v>
+        <v>21952.2087434223</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>BRB</t>
+          <t>BRN</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>24393.2193483944</v>
+        <v>81788.7819525501</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>BRN</t>
+          <t>BTN</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>36632.9280952155</v>
+        <v>15061.4232582306</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>BTN</t>
+          <t>BWA</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>3711.32767981591</v>
+        <v>19973.6684436048</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>BWA</t>
+          <t>CAF</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>8328.7090572666</v>
+        <v>1217.6567661451</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>CAF</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>467.359825026238</v>
+        <v>64217.0443455227</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>CAN</t>
+          <t>CHE</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>56496.9275340663</v>
+        <v>94629.7224204886</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>CHE</t>
+          <t>CHL</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>97809.095567203</v>
+        <v>30918.9258262719</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>CHI</t>
+          <t>CHN</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>67627.1417347907</v>
+        <v>23028.4517927066</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>CHL</t>
+          <t>CIV</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>15399.1044717559</v>
+        <v>6718.37891572875</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>CHN</t>
+          <t>CMR</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>12970.6056414327</v>
+        <v>5188.15515765322</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>CIV</t>
+          <t>COD</t>
         </is>
       </c>
       <c r="B39" t="n">
-        <v>2333.37128301259</v>
+        <v>1589.91203243059</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>CMR</t>
+          <t>COG</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>1604.87726954895</v>
+        <v>6646.44331964568</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>COD</t>
+          <t>COL</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>687.738587554685</v>
+        <v>20854.002999162</v>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>COG</t>
+          <t>COM</t>
         </is>
       </c>
       <c r="B42" t="n">
-        <v>2620.83804267402</v>
+        <v>3712.34821507981</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>COL</t>
+          <t>CPV</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>6680.44506854481</v>
+        <v>9479.570790166939</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>COM</t>
+          <t>CRI</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>1533.87755393614</v>
+        <v>26891.9730070246</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>CPV</t>
+          <t>CUW</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>4323.31362032709</v>
+        <v>28636.1483744106</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>CRI</t>
+          <t>CYM</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>13971.7649991294</v>
+        <v>82193.1801927387</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>CUW</t>
+          <t>CYP</t>
         </is>
       </c>
       <c r="B47" t="n">
-        <v>20057.1404960105</v>
+        <v>55876.3828125</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CYM</t>
+          <t>CZE</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>92937.8838323153</v>
+        <v>52946.9660854462</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>CYP</t>
+          <t>DEU</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>33231.05078125</v>
+        <v>69669.6495435563</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>CZE</t>
+          <t>DJI</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>28282.2236715857</v>
+        <v>6620.28103140186</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>DEU</t>
+          <t>DMA</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>50506.5179638543</v>
+        <v>18799.1022306558</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>DJI</t>
+          <t>DNK</t>
         </is>
       </c>
       <c r="B52" t="n">
-        <v>3133.25779772463</v>
+        <v>78554.12176179831</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>DMA</t>
+          <t>DOM</t>
         </is>
       </c>
       <c r="B53" t="n">
-        <v>9323.660894905621</v>
+        <v>24621.9061494267</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>DNK</t>
+          <t>DZA</t>
         </is>
       </c>
       <c r="B54" t="n">
-        <v>67781.0940939514</v>
+        <v>15833.5847271335</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>DOM</t>
+          <t>ECU</t>
         </is>
       </c>
       <c r="B55" t="n">
-        <v>10104.2464008585</v>
+        <v>15195.6639594842</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>DZA</t>
+          <t>EGY</t>
         </is>
       </c>
       <c r="B56" t="n">
-        <v>4960.30334332888</v>
+        <v>17524.0240491999</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>ECU</t>
+          <t>ESP</t>
         </is>
       </c>
       <c r="B57" t="n">
-        <v>6515.58528418336</v>
+        <v>51482.523634807</v>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>EGY</t>
+          <t>EST</t>
         </is>
       </c>
       <c r="B58" t="n">
-        <v>4233.30783744856</v>
+        <v>48029.83322897</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>ESP</t>
+          <t>ETH</t>
         </is>
       </c>
       <c r="B59" t="n">
-        <v>30319.4987196616</v>
+        <v>2844.47188098448</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>EST</t>
+          <t>FIN</t>
         </is>
       </c>
       <c r="B60" t="n">
-        <v>28340.3826549406</v>
+        <v>62133.1375219912</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>ETH</t>
+          <t>FJI</t>
         </is>
       </c>
       <c r="B61" t="n">
-        <v>982.103161502198</v>
+        <v>12980.234013809</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>FIN</t>
+          <t>FRA</t>
         </is>
       </c>
       <c r="B62" t="n">
-        <v>50440.560224974</v>
+        <v>57012.0586826676</v>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>FJI</t>
+          <t>FRO</t>
         </is>
       </c>
       <c r="B63" t="n">
-        <v>5414.12092119088</v>
+        <v>75266.29526904129</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>FRA</t>
+          <t>FSM</t>
         </is>
       </c>
       <c r="B64" t="n">
-        <v>40988.6396406579</v>
+        <v>4087.19316400156</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>FRO</t>
+          <t>GAB</t>
         </is>
       </c>
       <c r="B65" t="n">
-        <v>67069.39874405089</v>
+        <v>19989.3886367516</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>FSM</t>
+          <t>GBR</t>
         </is>
       </c>
       <c r="B66" t="n">
-        <v>3703.66680343222</v>
+        <v>60266.7467325014</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>GAB</t>
+          <t>GEO</t>
         </is>
       </c>
       <c r="B67" t="n">
-        <v>8409.207414522791</v>
+        <v>22457.7729614408</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>GBR</t>
+          <t>GHA</t>
         </is>
       </c>
       <c r="B68" t="n">
-        <v>47034.7795621476</v>
+        <v>7207.01563645025</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>GEO</t>
+          <t>GIN</t>
         </is>
       </c>
       <c r="B69" t="n">
-        <v>6729.84659930283</v>
+        <v>4061.71755990026</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>GHA</t>
+          <t>GMB</t>
         </is>
       </c>
       <c r="B70" t="n">
-        <v>2229.89122654479</v>
+        <v>3066.82429529872</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>GIN</t>
+          <t>GNB</t>
         </is>
       </c>
       <c r="B71" t="n">
-        <v>1416.59612011764</v>
+        <v>2785.7846268362</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>GMB</t>
+          <t>GNQ</t>
         </is>
       </c>
       <c r="B72" t="n">
-        <v>836.244875868476</v>
+        <v>18137.114494644</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>GNB</t>
+          <t>GRC</t>
         </is>
       </c>
       <c r="B73" t="n">
-        <v>881.602654162231</v>
+        <v>39447.813910406</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>GNQ</t>
+          <t>GRD</t>
         </is>
       </c>
       <c r="B74" t="n">
-        <v>7589.29964909381</v>
+        <v>17541.2011831673</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>GRC</t>
+          <t>GRL</t>
         </is>
       </c>
       <c r="B75" t="n">
-        <v>20884.6773436263</v>
+        <v>75708.4296211883</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>GRD</t>
+          <t>GTM</t>
         </is>
       </c>
       <c r="B76" t="n">
-        <v>10469.3867012856</v>
+        <v>13008.2565459863</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>GRL</t>
+          <t>GUY</t>
         </is>
       </c>
       <c r="B77" t="n">
-        <v>55635.0006491223</v>
+        <v>39704.6761521236</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>GTM</t>
+          <t>HKG</t>
         </is>
       </c>
       <c r="B78" t="n">
-        <v>5356.92435887895</v>
+        <v>68590.18587415649</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>GUM</t>
+          <t>HND</t>
         </is>
       </c>
       <c r="B79" t="n">
-        <v>41833.1517132825</v>
+        <v>6804.41504589356</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>GUY</t>
+          <t>HRV</t>
         </is>
       </c>
       <c r="B80" t="n">
-        <v>17913.4928066879</v>
+        <v>42125.1926231817</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>HKG</t>
+          <t>HTI</t>
         </is>
       </c>
       <c r="B81" t="n">
-        <v>48825.0272275805</v>
+        <v>3245.27176023069</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>HND</t>
+          <t>HUN</t>
         </is>
       </c>
       <c r="B82" t="n">
-        <v>3003.28996826399</v>
+        <v>44232.4363539167</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>HRV</t>
+          <t>IDN</t>
         </is>
       </c>
       <c r="B83" t="n">
-        <v>18465.531473659</v>
+        <v>14282.6654124401</v>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>HTI</t>
+          <t>IND</t>
         </is>
       </c>
       <c r="B84" t="n">
-        <v>1748.40890116803</v>
+        <v>8941.092774475141</v>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>HUN</t>
+          <t>IRL</t>
         </is>
       </c>
       <c r="B85" t="n">
-        <v>18428.028825614</v>
+        <v>138464.829172919</v>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>IDN</t>
+          <t>IRN</t>
         </is>
       </c>
       <c r="B86" t="n">
-        <v>4730.83484836107</v>
+        <v>17542.844026084</v>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>IMN</t>
+          <t>IRQ</t>
         </is>
       </c>
       <c r="B87" t="n">
-        <v>88328.548125887</v>
+        <v>14388.8485236797</v>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>IND</t>
+          <t>ISL</t>
         </is>
       </c>
       <c r="B88" t="n">
-        <v>2279.98145719369</v>
+        <v>76592.3392429534</v>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>IRL</t>
+          <t>ISR</t>
         </is>
       </c>
       <c r="B89" t="n">
-        <v>105190.685952731</v>
+        <v>53616.7140829107</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IRN</t>
+          <t>ITA</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>4721.20437099984</v>
+        <v>57260.8945372493</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>IRQ</t>
+          <t>JAM</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>6520.73154560584</v>
+        <v>11885.8863913319</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>ISL</t>
+          <t>JOR</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>76376.9599334915</v>
+        <v>10880.9956299022</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>ISR</t>
+          <t>JPN</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>54947.2091250715</v>
+        <v>49245.964174373</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>ITA</t>
+          <t>KAZ</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>35653.9042103495</v>
+        <v>35889.3953214448</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>JAM</t>
+          <t>KEN</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>6626.47502388538</v>
+        <v>5882.29066433207</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>JOR</t>
+          <t>KGZ</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>4754.41362207378</v>
+        <v>6576.46977080639</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>JPN</t>
+          <t>KHM</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>35548.2645222433</v>
+        <v>6917.7197730003</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>KAZ</t>
+          <t>KIR</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>11255.3396437881</v>
+        <v>3349.59804202737</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>KEN</t>
+          <t>KNA</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>2109.56288513137</v>
+        <v>31865.8304697944</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>KGZ</t>
+          <t>KOR</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>1739.72018344174</v>
+        <v>55509.3368761174</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>KHM</t>
+          <t>KWT</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>2325.03050040841</v>
+        <v>55034.2790289403</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>KIR</t>
+          <t>LAO</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>2078.7648751855</v>
+        <v>8765.051317471631</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>KNA</t>
+          <t>LBN</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>21011.5744209816</v>
+        <v>12290.8925567636</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>KOR</t>
+          <t>LBR</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>34822.4048404971</v>
+        <v>1691.30467616419</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>KWT</t>
+          <t>LBY</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>39981.7691035833</v>
+        <v>12264.4456986569</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>LAO</t>
+          <t>LCA</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>2046.40440255621</v>
+        <v>24433.7034481087</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>LBN</t>
+          <t>LKA</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>3654.35845534878</v>
+        <v>14191.4051912109</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>LBR</t>
+          <t>LSO</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>744.617175237387</v>
+        <v>2760.87343646139</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>LBY</t>
+          <t>LTU</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>5986.63694851258</v>
+        <v>50653.3394443751</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>LCA</t>
+          <t>LUX</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>12976.1489693474</v>
+        <v>146919.145398495</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>LIE</t>
+          <t>LVA</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>188055.003235348</v>
+        <v>40546.4638799692</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>LKA</t>
+          <t>MAC</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>3342.63650438046</v>
+        <v>64183.3559914099</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>LSO</t>
+          <t>MAR</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>1030.12582947757</v>
+        <v>9308.556640625</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>LTU</t>
+          <t>MDA</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>24946.5724005188</v>
+        <v>16442.1034354056</v>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>LUX</t>
+          <t>MDG</t>
         </is>
       </c>
       <c r="B115" t="n">
-        <v>123719.658915996</v>
+        <v>1716.40079421689</v>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>LVA</t>
+          <t>MDV</t>
         </is>
       </c>
       <c r="B116" t="n">
-        <v>20221.103686109</v>
+        <v>22876.8862033838</v>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>MAC</t>
+          <t>MEX</t>
         </is>
       </c>
       <c r="B117" t="n">
-        <v>36806.891255461</v>
+        <v>23135.4931593441</v>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>MHL</t>
         </is>
       </c>
       <c r="B118" t="n">
-        <v>3463.1376953125</v>
+        <v>7431.2014968892</v>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>MCO</t>
+          <t>MKD</t>
         </is>
       </c>
       <c r="B119" t="n">
-        <v>226052.060664649</v>
+        <v>24212.3733096953</v>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>MDA</t>
+          <t>MLI</t>
         </is>
       </c>
       <c r="B120" t="n">
-        <v>5744.29618434435</v>
+        <v>3013.94334673825</v>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>MDG</t>
+          <t>MLT</t>
         </is>
       </c>
       <c r="B121" t="n">
-        <v>504.059106969168</v>
+        <v>60623.0076694404</v>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>MDV</t>
+          <t>MMR</t>
         </is>
       </c>
       <c r="B122" t="n">
-        <v>11786.0191492983</v>
+        <v>5731.02947916374</v>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>MEX</t>
+          <t>MNE</t>
         </is>
       </c>
       <c r="B123" t="n">
-        <v>11405.7940469896</v>
+        <v>28049.7293227735</v>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>MHL</t>
+          <t>MNG</t>
         </is>
       </c>
       <c r="B124" t="n">
-        <v>6455.6603538189</v>
+        <v>16399.3900820069</v>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>MKD</t>
+          <t>MOZ</t>
         </is>
       </c>
       <c r="B125" t="n">
-        <v>7606.2375253797</v>
+        <v>1581.76710168717</v>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>MLI</t>
+          <t>MRT</t>
         </is>
       </c>
       <c r="B126" t="n">
-        <v>976.914116406452</v>
+        <v>6483.80020315347</v>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>MLT</t>
+          <t>MUS</t>
         </is>
       </c>
       <c r="B127" t="n">
-        <v>35658.8318250199</v>
+        <v>26783.5527116445</v>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>MMR</t>
+          <t>MWI</t>
         </is>
       </c>
       <c r="B128" t="n">
-        <v>1158.05005034332</v>
+        <v>1778.02399491871</v>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>MNE</t>
+          <t>MYS</t>
         </is>
       </c>
       <c r="B129" t="n">
-        <v>10038.1849482517</v>
+        <v>34414.4136245222</v>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>MNG</t>
+          <t>NAM</t>
         </is>
       </c>
       <c r="B130" t="n">
-        <v>4993.51487463495</v>
+        <v>10661.0118776397</v>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>MNP</t>
+          <t>NER</t>
         </is>
       </c>
       <c r="B131" t="n">
-        <v>23785.754590043</v>
+        <v>1847.58034360869</v>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>MOZ</t>
+          <t>NGA</t>
         </is>
       </c>
       <c r="B132" t="n">
-        <v>578.273222184503</v>
+        <v>8303.641931916851</v>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>MRT</t>
+          <t>NIC</t>
         </is>
       </c>
       <c r="B133" t="n">
-        <v>1961.28166648869</v>
+        <v>7795.45560731699</v>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>MUS</t>
+          <t>NLD</t>
         </is>
       </c>
       <c r="B134" t="n">
-        <v>10246.5017455553</v>
+        <v>78630.3599072098</v>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>MWI</t>
+          <t>NOR</t>
         </is>
       </c>
       <c r="B135" t="n">
-        <v>604.269740360317</v>
+        <v>129914.042717786</v>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>MYS</t>
+          <t>NPL</t>
         </is>
       </c>
       <c r="B136" t="n">
-        <v>11754.5678336248</v>
+        <v>5102.18358728663</v>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>NAM</t>
+          <t>NRU</t>
         </is>
       </c>
       <c r="B137" t="n">
-        <v>4349.79908493314</v>
+        <v>12874.2258577781</v>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>NCL</t>
+          <t>NZL</t>
         </is>
       </c>
       <c r="B138" t="n">
-        <v>33516.363085906</v>
+        <v>54080.0485491723</v>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>NER</t>
+          <t>OMN</t>
         </is>
       </c>
       <c r="B139" t="n">
-        <v>613.614736429298</v>
+        <v>42609.5810436221</v>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>NGA</t>
+          <t>PAK</t>
         </is>
       </c>
       <c r="B140" t="n">
-        <v>2899.16047469267</v>
+        <v>5919.33605935593</v>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>NIC</t>
+          <t>PAN</t>
         </is>
       </c>
       <c r="B141" t="n">
-        <v>2322.89069619459</v>
+        <v>36327.3867449699</v>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>NLD</t>
+          <t>PER</t>
         </is>
       </c>
       <c r="B142" t="n">
-        <v>59123.318556487</v>
+        <v>16673.6937563476</v>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>NOR</t>
+          <t>PHL</t>
         </is>
       </c>
       <c r="B143" t="n">
-        <v>113122.130765691</v>
+        <v>10129.7407504053</v>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>NPL</t>
+          <t>PLW</t>
         </is>
       </c>
       <c r="B144" t="n">
-        <v>1385.91066002922</v>
+        <v>17415.0224611906</v>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>NRU</t>
+          <t>PNG</t>
         </is>
       </c>
       <c r="B145" t="n">
-        <v>15309.8345351924</v>
+        <v>4419.49434920144</v>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>NZL</t>
+          <t>POL</t>
         </is>
       </c>
       <c r="B146" t="n">
-        <v>49141.6316294227</v>
+        <v>46777.5524519162</v>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>OMN</t>
+          <t>PRI</t>
         </is>
       </c>
       <c r="B147" t="n">
-        <v>23223.5829405935</v>
+        <v>45320.1718585525</v>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>PAK</t>
+          <t>PRT</t>
         </is>
       </c>
       <c r="B148" t="n">
-        <v>1538.3228133171</v>
+        <v>45250.0152469537</v>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>PAN</t>
+          <t>PRY</t>
         </is>
       </c>
       <c r="B149" t="n">
-        <v>17378.6070083597</v>
+        <v>16305.6206649067</v>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>PER</t>
+          <t>PSE</t>
         </is>
       </c>
       <c r="B150" t="n">
-        <v>7353.74598721667</v>
+        <v>6162.27222447827</v>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>PHL</t>
+          <t>QAT</t>
         </is>
       </c>
       <c r="B151" t="n">
-        <v>3548.06930572116</v>
+        <v>122901.018274888</v>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>PLW</t>
+          <t>ROU</t>
         </is>
       </c>
       <c r="B152" t="n">
-        <v>13934.951996171</v>
+        <v>41979.4260140907</v>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>PNG</t>
+          <t>RUS</t>
         </is>
       </c>
       <c r="B153" t="n">
-        <v>3102.29409730005</v>
+        <v>40932.71484375</v>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>POL</t>
+          <t>RWA</t>
         </is>
       </c>
       <c r="B154" t="n">
-        <v>18891.2121169279</v>
+        <v>3195.28136566525</v>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>PRI</t>
+          <t>SAU</t>
         </is>
       </c>
       <c r="B155" t="n">
-        <v>35353.5613891039</v>
+        <v>71956.6694296826</v>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>PRT</t>
+          <t>SDN</t>
         </is>
       </c>
       <c r="B156" t="n">
-        <v>24620.5197587181</v>
+        <v>3354.84643554688</v>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>PRY</t>
+          <t>SEN</t>
         </is>
       </c>
       <c r="B157" t="n">
-        <v>6189.10205375331</v>
+        <v>4529.50264399113</v>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>PSE</t>
+          <t>SGP</t>
         </is>
       </c>
       <c r="B158" t="n">
-        <v>3799.95527015163</v>
+        <v>144417.646950009</v>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>PYF</t>
+          <t>SLB</t>
         </is>
       </c>
       <c r="B159" t="n">
-        <v>20053.9569369322</v>
+        <v>2496.15153066833</v>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>QAT</t>
+          <t>SLE</t>
         </is>
       </c>
       <c r="B160" t="n">
-        <v>88701.463352273</v>
+        <v>3143.46625292281</v>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>ROU</t>
+          <t>SLV</t>
         </is>
       </c>
       <c r="B161" t="n">
-        <v>15503.4691366242</v>
+        <v>11874.0814242931</v>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>RUS</t>
+          <t>SMR</t>
         </is>
       </c>
       <c r="B162" t="n">
-        <v>15625.6328125</v>
+        <v>75929.4591270254</v>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>RWA</t>
+          <t>SOM</t>
         </is>
       </c>
       <c r="B163" t="n">
-        <v>1007.05989322914</v>
+        <v>1486.23689665021</v>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>SAU</t>
+          <t>SRB</t>
         </is>
       </c>
       <c r="B164" t="n">
-        <v>38510.2276211037</v>
+        <v>26142.9143111159</v>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>SDN</t>
+          <t>STP</t>
         </is>
       </c>
       <c r="B165" t="n">
-        <v>1046.24084472656</v>
+        <v>6032.7249522726</v>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>SEN</t>
+          <t>SUR</t>
         </is>
       </c>
       <c r="B166" t="n">
-        <v>1574.0281059306</v>
+        <v>20075.6544534114</v>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>SGP</t>
+          <t>SVK</t>
         </is>
       </c>
       <c r="B167" t="n">
-        <v>91227.6970426492</v>
+        <v>41529.408474315</v>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>SLB</t>
+          <t>SVN</t>
         </is>
       </c>
       <c r="B168" t="n">
-        <v>1877.78104490956</v>
+        <v>52322.1405997493</v>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>SLE</t>
+          <t>SWE</t>
         </is>
       </c>
       <c r="B169" t="n">
-        <v>860.371067874555</v>
+        <v>66517.6358713011</v>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>SLV</t>
+          <t>SWZ</t>
         </is>
       </c>
       <c r="B170" t="n">
-        <v>5074.60050994225</v>
+        <v>10633.7069148254</v>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>SMR</t>
+          <t>SXM</t>
         </is>
       </c>
       <c r="B171" t="n">
-        <v>54264.5837022908</v>
+        <v>48752.9549877316</v>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>SOM</t>
+          <t>SYC</t>
         </is>
       </c>
       <c r="B172" t="n">
-        <v>573.1411657982291</v>
+        <v>29215.6725189214</v>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>SRB</t>
+          <t>SYR</t>
         </is>
       </c>
       <c r="B173" t="n">
-        <v>10024.8191112596</v>
+        <v>4905.15252202552</v>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>STP</t>
+          <t>TCA</t>
         </is>
       </c>
       <c r="B174" t="n">
-        <v>2389.73729784737</v>
+        <v>30216.0346068372</v>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>SUR</t>
+          <t>TCD</t>
         </is>
       </c>
       <c r="B175" t="n">
-        <v>6084.43876736445</v>
+        <v>2623.702025997</v>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>SVK</t>
+          <t>TGO</t>
         </is>
       </c>
       <c r="B176" t="n">
-        <v>21317.7943982363</v>
+        <v>3305.92970304109</v>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>SVN</t>
+          <t>THA</t>
         </is>
       </c>
       <c r="B177" t="n">
-        <v>28360.3041467268</v>
+        <v>22245.6387597542</v>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>SWE</t>
+          <t>TJK</t>
         </is>
       </c>
       <c r="B178" t="n">
-        <v>54836.8907235124</v>
+        <v>4513.4597158968</v>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>SWZ</t>
+          <t>TKM</t>
         </is>
       </c>
       <c r="B179" t="n">
-        <v>3894.1620089869</v>
+        <v>18148.7189785918</v>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>SXM</t>
+          <t>TLS</t>
         </is>
       </c>
       <c r="B180" t="n">
-        <v>37793.1283815826</v>
+        <v>5728.90346523347</v>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>SYC</t>
+          <t>TON</t>
         </is>
       </c>
       <c r="B181" t="n">
-        <v>16682.6990711785</v>
+        <v>7295.94922827877</v>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>SYR</t>
+          <t>TTO</t>
         </is>
       </c>
       <c r="B182" t="n">
-        <v>1056.78264718197</v>
+        <v>32973.632075038</v>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>TCA</t>
+          <t>TUN</t>
         </is>
       </c>
       <c r="B183" t="n">
-        <v>31280.5418020808</v>
+        <v>13616.380720945</v>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>TCD</t>
+          <t>TUR</t>
         </is>
       </c>
       <c r="B184" t="n">
-        <v>966.036468278568</v>
+        <v>39919.1608756567</v>
       </c>
     </row>
     <row r="185">
       <c r="A185" t="inlineStr">
         <is>
-          <t>TGO</t>
+          <t>TUV</t>
         </is>
       </c>
       <c r="B185" t="n">
-        <v>1071.61539220759</v>
+        <v>5403.33289042089</v>
       </c>
     </row>
     <row r="186">
       <c r="A186" t="inlineStr">
         <is>
-          <t>THA</t>
+          <t>TZA</t>
         </is>
       </c>
       <c r="B186" t="n">
-        <v>6910.00995211206</v>
+        <v>3799.26000976563</v>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>TJK</t>
+          <t>UGA</t>
         </is>
       </c>
       <c r="B187" t="n">
-        <v>1052.17949484894</v>
+        <v>2918.71512173871</v>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>TKM</t>
+          <t>UKR</t>
         </is>
       </c>
       <c r="B188" t="n">
-        <v>5198.18947409551</v>
+        <v>14767.73046875</v>
       </c>
     </row>
     <row r="189">
       <c r="A189" t="inlineStr">
         <is>
-          <t>TLS</t>
+          <t>URY</t>
         </is>
       </c>
       <c r="B189" t="n">
-        <v>2343.24955542816</v>
+        <v>33033.5719368346</v>
       </c>
     </row>
     <row r="190">
       <c r="A190" t="inlineStr">
         <is>
-          <t>TON</t>
+          <t>USA</t>
         </is>
       </c>
       <c r="B190" t="n">
-        <v>5298.01942454298</v>
+        <v>78008.6895811877</v>
       </c>
     </row>
     <row r="191">
       <c r="A191" t="inlineStr">
         <is>
-          <t>TTO</t>
+          <t>UZB</t>
         </is>
       </c>
       <c r="B191" t="n">
-        <v>20750.5202434652</v>
+        <v>10809.1380396181</v>
       </c>
     </row>
     <row r="192">
       <c r="A192" t="inlineStr">
         <is>
-          <t>TUN</t>
+          <t>VCT</t>
         </is>
       </c>
       <c r="B192" t="n">
-        <v>3707.29283414381</v>
+        <v>18032.4150562634</v>
       </c>
     </row>
     <row r="193">
       <c r="A193" t="inlineStr">
         <is>
-          <t>TUR</t>
+          <t>VIR</t>
         </is>
       </c>
       <c r="B193" t="n">
-        <v>10897.8397861365</v>
+        <v>49785.1412220186</v>
       </c>
     </row>
     <row r="194">
       <c r="A194" t="inlineStr">
         <is>
-          <t>TUV</t>
+          <t>VNM</t>
         </is>
       </c>
       <c r="B194" t="n">
-        <v>5414.74642912412</v>
+        <v>13902.9499867089</v>
       </c>
     </row>
     <row r="195">
       <c r="A195" t="inlineStr">
         <is>
-          <t>TZA</t>
+          <t>VUT</t>
         </is>
       </c>
       <c r="B195" t="n">
-        <v>1207.52062988281</v>
+        <v>3918.73096260725</v>
       </c>
     </row>
     <row r="196">
       <c r="A196" t="inlineStr">
         <is>
-          <t>UGA</t>
+          <t>WSM</t>
         </is>
       </c>
       <c r="B196" t="n">
-        <v>963.0673141171779</v>
+        <v>6908.96157777708</v>
       </c>
     </row>
     <row r="197">
       <c r="A197" t="inlineStr">
         <is>
-          <t>UKR</t>
+          <t>XKX</t>
         </is>
       </c>
       <c r="B197" t="n">
-        <v>4199.6708984375</v>
+        <v>13948.6857891476</v>
       </c>
     </row>
     <row r="198">
       <c r="A198" t="inlineStr">
         <is>
-          <t>URY</t>
+          <t>ZAF</t>
         </is>
       </c>
       <c r="B198" t="n">
-        <v>21009.2883798725</v>
+        <v>14746.7103701698</v>
       </c>
     </row>
     <row r="199">
       <c r="A199" t="inlineStr">
         <is>
-          <t>USA</t>
+          <t>ZMB</t>
         </is>
       </c>
       <c r="B199" t="n">
-        <v>78008.6895811877</v>
+        <v>3840.115825721</v>
       </c>
     </row>
     <row r="200">
       <c r="A200" t="inlineStr">
         <is>
-          <t>UZB</t>
+          <t>ZWE</t>
         </is>
       </c>
       <c r="B200" t="n">
-        <v>2698.60262953369</v>
-      </c>
-    </row>
-    <row r="201">
-      <c r="A201" t="inlineStr">
-        <is>
-          <t>VCT</t>
-        </is>
-      </c>
-      <c r="B201" t="n">
-        <v>9693.55867833025</v>
-      </c>
-    </row>
-    <row r="202">
-      <c r="A202" t="inlineStr">
-        <is>
-          <t>VEN</t>
-        </is>
-      </c>
-      <c r="B202" t="n">
-        <v>3155.04190923584</v>
-      </c>
-    </row>
-    <row r="203">
-      <c r="A203" t="inlineStr">
-        <is>
-          <t>VIR</t>
-        </is>
-      </c>
-      <c r="B203" t="n">
-        <v>44320.909185774</v>
-      </c>
-    </row>
-    <row r="204">
-      <c r="A204" t="inlineStr">
-        <is>
-          <t>VNM</t>
-        </is>
-      </c>
-      <c r="B204" t="n">
-        <v>4147.69777213621</v>
-      </c>
-    </row>
-    <row r="205">
-      <c r="A205" t="inlineStr">
-        <is>
-          <t>VUT</t>
-        </is>
-      </c>
-      <c r="B205" t="n">
-        <v>3679.53524327491</v>
-      </c>
-    </row>
-    <row r="206">
-      <c r="A206" t="inlineStr">
-        <is>
-          <t>WSM</t>
-        </is>
-      </c>
-      <c r="B206" t="n">
-        <v>4132.44717734444</v>
-      </c>
-    </row>
-    <row r="207">
-      <c r="A207" t="inlineStr">
-        <is>
-          <t>XKX</t>
-        </is>
-      </c>
-      <c r="B207" t="n">
-        <v>5298.1473871027</v>
-      </c>
-    </row>
-    <row r="208">
-      <c r="A208" t="inlineStr">
-        <is>
-          <t>ZAF</t>
-        </is>
-      </c>
-      <c r="B208" t="n">
-        <v>6534.24867783397</v>
-      </c>
-    </row>
-    <row r="209">
-      <c r="A209" t="inlineStr">
-        <is>
-          <t>ZMB</t>
-        </is>
-      </c>
-      <c r="B209" t="n">
-        <v>1447.12310138035</v>
-      </c>
-    </row>
-    <row r="210">
-      <c r="A210" t="inlineStr">
-        <is>
-          <t>ZWE</t>
-        </is>
-      </c>
-      <c r="B210" t="n">
-        <v>2536.40197087505</v>
+        <v>5395.02452868174</v>
       </c>
     </row>
   </sheetData>
@@ -7852,7 +7622,7 @@
   <cols>
     <col width="15" customWidth="1" min="1" max="1"/>
     <col width="23" customWidth="1" min="2" max="2"/>
-    <col width="48" customWidth="1" min="3" max="3"/>
+    <col width="47" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
     <col width="10" customWidth="1" min="5" max="5"/>
   </cols>
@@ -7895,14 +7665,14 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>9.2269, 37.1209</t>
+          <t>11.834, 23.0457</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.695</v>
+        <v>0.7184</v>
       </c>
       <c r="E2" t="n">
-        <v>0.6936</v>
+        <v>0.7169</v>
       </c>
     </row>
     <row r="3">
@@ -7916,14 +7686,14 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.538868, 13.4453, 29.0801</t>
+          <t>0.40116, 8.49851, 29.8774</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.7186</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6932</v>
+        <v>0.7157</v>
       </c>
     </row>
     <row r="4">
@@ -7937,14 +7707,14 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.593383, 6.41081, -13.175, 62.3896</t>
+          <t>-1.37156, 17.4532, -61.4525, 124.508</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.6969</v>
+        <v>0.7194</v>
       </c>
       <c r="E4" t="n">
-        <v>0.6924</v>
+        <v>0.7151</v>
       </c>
     </row>
     <row r="5">
@@ -7958,14 +7728,14 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>0.676026, -11.2044, 67.9071, -169.004, 207.958</t>
+          <t>-1.96341, 31.159, -183.026, 483.059, -425.308</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.6975</v>
+        <v>0.72</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6915</v>
+        <v>0.7141999999999999</v>
       </c>
     </row>
     <row r="6">
@@ -7982,7 +7752,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr"/>
@@ -7995,7 +7765,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.8337</v>
+        <v>0.8476</v>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr"/>
@@ -8008,7 +7778,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>5.014210083597042e-55</v>
+        <v>7.848304439746263e-56</v>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr"/>
@@ -8037,7 +7807,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>y = 9.23·log x + 37.1</t>
+          <t>y = 11.8·log x + 23</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>

--- a/003/xy_003_data.xlsx
+++ b/003/xy_003_data.xlsx
@@ -421,7 +421,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B31"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>14/10/2026</t>
+          <t>27/09/2026</t>
         </is>
       </c>
     </row>
@@ -472,7 +472,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>The Most Reassuring Chart on Earth</t>
+          <t>Income vs Life Expectancy</t>
         </is>
       </c>
     </row>
@@ -484,293 +484,281 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Richer countries live longer, but every extra dollar buys less time.</t>
+          <t>Richer countries live longer.</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>verdict</t>
+          <t>publication</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Income predicts longevity, with sharply diminishing returns in dollars.</t>
+          <t>https://xandyregression.substack.com</t>
         </is>
       </c>
     </row>
     <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>publication</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>https://xandyregression.substack.com</t>
-        </is>
-      </c>
+      <c r="A7" t="inlineStr"/>
+      <c r="B7" t="inlineStr"/>
     </row>
     <row r="8">
-      <c r="A8" t="inlineStr"/>
-      <c r="B8" t="inlineStr"/>
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>X label</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>GDP per capita (PPP $, World Bank)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>X label</t>
+          <t>X detail</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>GDP per capita (PPP $, World Bank)</t>
+          <t>GDP per capita, PPP, current international $, 2022, World Bank NY.GDP.PCAP.PP.CD, all countries with data</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>X detail</t>
+          <t>X source</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>GDP per capita, PPP, current international $, 2022, World Bank NY.GDP.PCAP.PP.CD, all countries with data</t>
+          <t>World Bank NY.GDP.PCAP.PP.CD (2022)</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>X source</t>
+          <t>X source URL</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>World Bank NY.GDP.PCAP.PP.CD (2022)</t>
+          <t>https://data.worldbank.org/indicator/NY.GDP.PCAP.PP.CD</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>X source URL</t>
+          <t>X licence</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://data.worldbank.org/indicator/NY.GDP.PCAP.PP.CD</t>
+          <t>open data, redistributed with attribution</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>X licence</t>
+          <t>X pulled</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>open data, redistributed with attribution</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>X pulled</t>
+          <t>X steps</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>25/09/2026 02:03</t>
+          <t>none</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>X steps</t>
+          <t>X raw sheet</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>none</t>
+          <t>full series as pulled, before any transform</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>X raw sheet</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>full series as pulled, before any transform</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
+      <c r="B16" t="inlineStr"/>
     </row>
     <row r="17">
-      <c r="A17" t="inlineStr"/>
-      <c r="B17" t="inlineStr"/>
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Y label</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Life expectancy at birth (years)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Y label</t>
+          <t>Y detail</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Life expectancy at birth (years)</t>
+          <t>Life expectancy at birth, total, years, 2022, World Bank SP.DYN.LE00.IN</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Y detail</t>
+          <t>Y source</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Life expectancy at birth, total, years, 2022, World Bank SP.DYN.LE00.IN</t>
+          <t>World Bank SP.DYN.LE00.IN (2022)</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Y source</t>
+          <t>Y source URL</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>World Bank SP.DYN.LE00.IN (2022)</t>
+          <t>https://data.worldbank.org/indicator/SP.DYN.LE00.IN</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Y source URL</t>
+          <t>Y licence</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://data.worldbank.org/indicator/SP.DYN.LE00.IN</t>
+          <t>open data, redistributed with attribution</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Y licence</t>
+          <t>Y pulled</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>open data, redistributed with attribution</t>
+          <t>26/09/2026 19:05</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Y pulled</t>
+          <t>Y steps</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>25/09/2026 02:03</t>
+          <t>dropped values below 40</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Y steps</t>
+          <t>Y raw sheet</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>dropped values below 40</t>
+          <t>full series as pulled, before any transform</t>
         </is>
       </c>
     </row>
     <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>Y raw sheet</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>full series as pulled, before any transform</t>
-        </is>
-      </c>
+      <c r="A25" t="inlineStr"/>
+      <c r="B25" t="inlineStr"/>
     </row>
     <row r="26">
-      <c r="A26" t="inlineStr"/>
-      <c r="B26" t="inlineStr"/>
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>join</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>on key</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>join</t>
+          <t>lag</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>on key</t>
+          <t>X leads Y by 0 periods</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>lag</t>
+          <t>transform</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>X leads Y by 0 periods</t>
+          <t>log_x</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>transform</t>
+          <t>p-value</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>log_x</t>
+          <t>OLS</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>p-value</t>
+          <t>note</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
-        <is>
-          <t>OLS</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>note</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
         <is>
           <t>correlation is not causation</t>
         </is>
